--- a/artfynd/A 9277-2023 artfynd.xlsx
+++ b/artfynd/A 9277-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73898151</v>
+        <v>137442471</v>
       </c>
       <c r="B2" t="n">
-        <v>99156</v>
+        <v>96656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219875</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storekullen, V om, Vg</t>
+          <t>Rosenlund, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424030</v>
+        <v>424164</v>
       </c>
       <c r="R2" t="n">
-        <v>6471554</v>
+        <v>6471552</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-08-29</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-08-29</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,34 +763,369 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Johan Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Johan Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering längs väg 49, Varnhem</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137442471</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137442376</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58196</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rosenlund, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>424035</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6471549</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skara</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Varnhem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Johan Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johan Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering längs väg 49, Varnhem</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137442376</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>73898151</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Storekullen, V om, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>424030</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6471554</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skara</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Varnhem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2010-08-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2010-08-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Karin Kjellberg</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Karin Kjellberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Billingens flora</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/73898151</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137442411</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101549</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rosenlund, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>424135</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6471570</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skara</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Varnhem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johan Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering längs väg 49, Varnhem</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137442411</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9277-2023 artfynd.xlsx
+++ b/artfynd/A 9277-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137442471</v>
       </c>
       <c r="B2" t="n">
-        <v>96656</v>
+        <v>96659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Naturvärdesinventering längs väg 49, Varnhem</t>
+          <t>Naturvärdesinventering längs väg 49, Varnhem - Storekullen</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Naturvärdesinventering längs väg 49, Varnhem</t>
+          <t>Naturvärdesinventering längs väg 49, Varnhem - Storekullen</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1014,7 +1014,7 @@
         <v>137442411</v>
       </c>
       <c r="B5" t="n">
-        <v>101549</v>
+        <v>101552</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Naturvärdesinventering längs väg 49, Varnhem</t>
+          <t>Naturvärdesinventering längs väg 49, Varnhem - Storekullen</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">

--- a/artfynd/A 9277-2023 artfynd.xlsx
+++ b/artfynd/A 9277-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137442471</v>
       </c>
       <c r="B2" t="n">
-        <v>96659</v>
+        <v>96663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137442376</v>
       </c>
       <c r="B3" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>137442411</v>
       </c>
       <c r="B5" t="n">
-        <v>101552</v>
+        <v>101556</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
